--- a/data/trans_camb/IP21B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 0,0</t>
+          <t>-69,21; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-64,64; 0,0</t>
+          <t>-69,21; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-31,04; 77,58</t>
+          <t>-30,61; 77,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-41,87; 21,24</t>
+          <t>-43,81; 20,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 40,31</t>
+          <t>-31,74; 43,54</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,94; 0,0</t>
+          <t>-57,01; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-33,42; 12,14</t>
+          <t>-37,12; 7,85</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-23,13; 26,75</t>
+          <t>-24,56; 22,36</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-27,33; 28,84</t>
+          <t>-27,21; 28,77</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-10,45; 41,51</t>
+          <t>-8,17; 43,24</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 45,76</t>
+          <t>-8,55; 46,78</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 0,0</t>
+          <t>-32,27; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,23; 39,98</t>
+          <t>-20,02; 39,8</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-20,87; 37,42</t>
+          <t>-26,31; 37,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 66,6</t>
+          <t>-19,93; 65,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 30,64</t>
+          <t>-3,91; 32,09</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,48; 31,8</t>
+          <t>-9,79; 31,66</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,42; 48,99</t>
+          <t>-15,01; 46,53</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-49,18; 713,98</t>
+          <t>-47,34; 752,27</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-65,95; 791,99</t>
+          <t>-69,71; 605,62</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1152,25</t>
         </is>
       </c>
     </row>
@@ -1119,17 +1119,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 82,28</t>
+          <t>0,0; 78,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-22,15; 32,92</t>
+          <t>-19,17; 32,6</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,54; 90,33</t>
+          <t>-10,11; 90,14</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 22,37</t>
+          <t>-10,85; 24,47</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,13; 58,21</t>
+          <t>-5,22; 60,14</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,11; 77,66</t>
+          <t>-5,26; 73,92</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-48,1; 38,14</t>
+          <t>-48,96; 38,72</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-39,27; 65,6</t>
+          <t>-30,6; 69,93</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,32 +1340,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-14,99; 42,78</t>
+          <t>-15,96; 39,65</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,93; 42,61</t>
+          <t>-18,97; 49,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,2; 68,27</t>
+          <t>-11,99; 73,07</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,81; 28,58</t>
+          <t>-15,11; 28,23</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-13,61; 42,34</t>
+          <t>-8,17; 46,74</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-14,36; 59,6</t>
+          <t>-18,95; 64,14</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-78,06; 708,38</t>
+          <t>-74,37; 842,39</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-77,54; 982,63</t>
+          <t>-70,46; inf</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,84; 20,88</t>
+          <t>-7,78; 21,33</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 30,65</t>
+          <t>-3,51; 30,35</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 47,15</t>
+          <t>-5,67; 41,03</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 21,64</t>
+          <t>-8,2; 20,11</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 29,06</t>
+          <t>-6,48; 29,33</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 44,01</t>
+          <t>-7,64; 38,87</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,16; 16,49</t>
+          <t>-4,42; 16,19</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,7; 23,43</t>
+          <t>-0,94; 24,29</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 32,18</t>
+          <t>0,4; 33,25</t>
         </is>
       </c>
     </row>
@@ -1647,12 +1647,12 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-65,48; 625,71</t>
+          <t>-61,76; 629,33</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-36,55; 906,0</t>
+          <t>-41,59; 775,36</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
@@ -1662,32 +1662,32 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-45,6; 462,12</t>
+          <t>-47,05; 352,22</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-50,28; 449,94</t>
+          <t>-46,07; 475,78</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-50,02; 824,56</t>
+          <t>-62,86; 651,79</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-29,11; 260,46</t>
+          <t>-31,17; 247,41</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-17,47; 356,3</t>
+          <t>-11,46; 360,51</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-12,32; 477,27</t>
+          <t>-9,88; 472,79</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Habitat-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-69,21; 0,0</t>
+          <t>-72,51; 0,0</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-69,21; 0,0</t>
+          <t>-72,51; 0,0</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,61; 77,58</t>
+          <t>-30,69; 77,58</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 20,99</t>
+          <t>-43,99; 20,57</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-31,74; 43,54</t>
+          <t>-32,88; 43,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-57,01; 0,0</t>
+          <t>-54,55; 0,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-37,12; 7,85</t>
+          <t>-36,67; 6,7</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-24,56; 22,36</t>
+          <t>-28,32; 22,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-27,21; 28,77</t>
+          <t>-27,57; 29,06</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 43,24</t>
+          <t>-8,81; 40,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 46,78</t>
+          <t>-7,74; 45,25</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-32,27; 0,0</t>
+          <t>-36,93; 0,0</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-20,02; 39,8</t>
+          <t>-19,78; 43,16</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,31; 37,08</t>
+          <t>-26,56; 37,21</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-19,93; 65,61</t>
+          <t>-20,6; 65,61</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 32,09</t>
+          <t>-5,66; 33,12</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-9,79; 31,66</t>
+          <t>-10,49; 31,48</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 46,53</t>
+          <t>-12,16; 48,98</t>
         </is>
       </c>
     </row>
@@ -999,12 +999,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-47,34; 752,27</t>
+          <t>-52,16; 700,05</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-69,71; 605,62</t>
+          <t>-67,47; 755,68</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1152,25</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -1119,17 +1119,17 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,15</t>
+          <t>0,0; 78,14</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,17; 32,6</t>
+          <t>-19,66; 33,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-10,11; 90,14</t>
+          <t>-19,18; 100,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1139,17 +1139,17 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,85; 24,47</t>
+          <t>-10,36; 24,67</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,22; 60,14</t>
+          <t>-5,37; 56,0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 73,92</t>
+          <t>-5,19; 72,01</t>
         </is>
       </c>
     </row>
@@ -1325,12 +1325,12 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-48,96; 38,72</t>
+          <t>-47,8; 37,87</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-30,6; 69,93</t>
+          <t>-30,76; 68,82</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
@@ -1340,32 +1340,32 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-15,96; 39,65</t>
+          <t>-17,94; 39,86</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-18,97; 49,42</t>
+          <t>-19,41; 47,64</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-11,99; 73,07</t>
+          <t>-12,16; 72,15</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-15,11; 28,23</t>
+          <t>-16,88; 28,05</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 46,74</t>
+          <t>-10,91; 44,39</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,95; 64,14</t>
+          <t>-9,7; 64,45</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-74,37; 842,39</t>
+          <t>-81,54; 789,36</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-70,46; inf</t>
+          <t>-67,97; 1083,77</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-7,78; 21,33</t>
+          <t>-9,02; 19,5</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,51; 30,35</t>
+          <t>-3,29; 31,01</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-5,67; 41,03</t>
+          <t>-6,28; 45,9</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,2; 20,11</t>
+          <t>-7,6; 20,09</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,48; 29,33</t>
+          <t>-7,92; 26,83</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 38,87</t>
+          <t>-7,43; 41,92</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 16,19</t>
+          <t>-4,8; 15,74</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-0,94; 24,29</t>
+          <t>-1,65; 24,08</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>0,4; 33,25</t>
+          <t>-2,7; 34,41</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-61,76; 629,33</t>
+          <t>-66,93; 562,02</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-41,59; 775,36</t>
+          <t>-37,11; 952,86</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 1532,13</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-47,05; 352,22</t>
+          <t>-46,4; 344,24</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-46,07; 475,78</t>
+          <t>-56,42; 418,45</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-62,86; 651,79</t>
+          <t>-49,91; 645,39</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-31,17; 247,41</t>
+          <t>-34,52; 237,55</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-11,46; 360,51</t>
+          <t>-15,38; 346,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 472,79</t>
+          <t>-27,59; 447,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP21B-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IP21B-Habitat-trans_camb.xlsx
@@ -523,20 +523,20 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que estuvieron en lista de espera para ser ingresados</t>
+          <t>Menores que, en los últimos 12 meses, estuvieron en lista de espera para ingresar, al menos una noche, en un hospital</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-3,79</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>8,49</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-13,64</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>-14,93</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>-14,93</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>14,65</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-3,79</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>8,49</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-13,64</t>
+          <t>17,73</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-2,66</t>
+          <t>-0,57</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-72,51; 0,0</t>
+          <t>-41,87; 21,24</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-72,51; 0,0</t>
+          <t>-31,66; 40,31</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-30,69; 77,58</t>
+          <t>-57,94; 0,0</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-43,99; 20,57</t>
+          <t>-64,64; 0,0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-32,88; 43,0</t>
+          <t>-64,64; 0,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-54,55; 0,0</t>
+          <t>-31,04; 78,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-36,67; 6,7</t>
+          <t>-33,42; 12,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-28,32; 22,34</t>
+          <t>-23,13; 26,75</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-27,57; 29,06</t>
+          <t>-27,15; 34,92</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-27,76%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>62,21%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>98,12%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>-27,76%</t>
-        </is>
-      </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>-100,0%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-100,0%</t>
+          <t>118,7%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-18,76%</t>
+          <t>-4,03%</t>
         </is>
       </c>
     </row>
@@ -840,34 +840,34 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6,18</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>-0,25</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>16,68</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>15,04</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>17,7</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>-10,63</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>6,18</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>-0,25</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>16,5</t>
-        </is>
-      </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
           <t>11,39</t>
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>9,33</t>
+          <t>9,62</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 40,91</t>
+          <t>-20,23; 39,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-7,74; 45,25</t>
+          <t>-20,87; 37,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-36,93; 0,0</t>
+          <t>-20,15; 69,33</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-19,78; 43,16</t>
+          <t>-10,45; 41,51</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-26,56; 37,21</t>
+          <t>-6,87; 45,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-20,6; 65,61</t>
+          <t>-37,11; 0,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 33,12</t>
+          <t>-6,45; 30,64</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-10,49; 31,48</t>
+          <t>-9,48; 31,8</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 48,98</t>
+          <t>-12,6; 50,83</t>
         </is>
       </c>
     </row>
@@ -946,34 +946,34 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>46,02%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>-1,88%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>124,17%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>141,53%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>166,57%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>46,02%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-1,88%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>122,84%</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
           <t>95,39%</t>
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>80,57%</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-52,16; 700,05</t>
+          <t>-49,18; 713,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-67,47; 755,68</t>
+          <t>-65,95; 791,99</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>9,46</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>38,72</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,0</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36,45</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>9,46</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>38,72</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>39,16</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>31,29</t>
+          <t>34,01</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-22,15; 32,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-10,54; 90,33</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 78,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-19,66; 33,55</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-19,18; 100,0</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 84,71</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,36; 24,67</t>
+          <t>-7,45; 22,37</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-5,37; 56,0</t>
+          <t>-5,13; 58,21</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-5,19; 72,01</t>
+          <t>-5,1; 80,28</t>
         </is>
       </c>
     </row>
@@ -1162,34 +1162,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>96,03%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>393,06%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>inf%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>96,03%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>393,06%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>144,49%</t>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>606,43%</t>
+          <t>659,13%</t>
         </is>
       </c>
     </row>
@@ -1272,34 +1272,34 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>9,48</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>1,22</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>27,55</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,1</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>23,59</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>-19,06</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>9,48</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>26,6</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
           <t>6,99</t>
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>19,43</t>
+          <t>19,99</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-47,8; 37,87</t>
+          <t>-14,99; 42,78</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-30,76; 68,82</t>
+          <t>-18,93; 42,61</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-12,24; 70,17</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-17,94; 39,86</t>
+          <t>-48,1; 38,14</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 47,64</t>
+          <t>-39,27; 65,6</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-12,16; 72,15</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-16,88; 28,05</t>
+          <t>-15,81; 28,58</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-10,91; 44,39</t>
+          <t>-13,61; 42,34</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-9,7; 64,45</t>
+          <t>-14,47; 60,03</t>
         </is>
       </c>
     </row>
@@ -1378,34 +1378,34 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>77,63%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>9,97%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>225,61%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>5,77%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>123,78%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>-100,0%</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>77,63%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>9,97%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>217,87%</t>
-        </is>
-      </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
           <t>50,02%</t>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>139,02%</t>
+          <t>143,03%</t>
         </is>
       </c>
     </row>
@@ -1461,12 +1461,12 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-81,54; 789,36</t>
+          <t>-78,06; 708,38</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>-67,97; 1083,77</t>
+          <t>-77,54; 982,63</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -1488,32 +1488,32 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>5,75</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>8,96</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>14,21</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
           <t>5,81</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>12,79</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>14,62</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>5,75</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>8,96</t>
-        </is>
-      </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>13,41</t>
+          <t>16,96</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>13,95</t>
+          <t>15,4</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-9,02; 19,5</t>
+          <t>-7,8; 21,64</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-3,29; 31,01</t>
+          <t>-8,19; 29,06</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 45,9</t>
+          <t>-6,51; 45,83</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-7,6; 20,09</t>
+          <t>-7,84; 20,88</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-7,92; 26,83</t>
+          <t>-2,99; 30,65</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 41,92</t>
+          <t>-4,35; 49,43</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,8; 15,74</t>
+          <t>-4,16; 16,49</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-1,65; 24,08</t>
+          <t>-1,7; 23,43</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,7; 34,41</t>
+          <t>-0,76; 34,46</t>
         </is>
       </c>
     </row>
@@ -1594,32 +1594,32 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>46,89%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>72,98%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>115,78%</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
           <t>59,82%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr">
         <is>
           <t>131,59%</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>150,45%</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>46,89%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>72,98%</t>
-        </is>
-      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>109,29%</t>
+          <t>174,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>124,94%</t>
+          <t>137,97%</t>
         </is>
       </c>
     </row>
@@ -1647,47 +1647,47 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-66,93; 562,02</t>
+          <t>-45,6; 462,12</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-37,11; 952,86</t>
+          <t>-50,28; 449,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 1532,13</t>
+          <t>-47,43; 887,35</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-46,4; 344,24</t>
+          <t>-65,48; 625,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-56,42; 418,45</t>
+          <t>-36,55; 906,0</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-49,91; 645,39</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-34,52; 237,55</t>
+          <t>-29,11; 260,46</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-15,38; 346,3</t>
+          <t>-17,47; 356,3</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 447,08</t>
+          <t>-6,84; 527,77</t>
         </is>
       </c>
     </row>
